--- a/Descomissionamento/Dados/ANP_descomissionamento.xlsx
+++ b/Descomissionamento/Dados/ANP_descomissionamento.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LaTex_Projects\Descomissionamento\Dados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LaTex_Projects\Descomissionamento\Dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953B3088-3720-484C-932F-5515F4CA8D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9129601C-A271-4CA4-8953-641250654F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="atividade-realizada-2022-2024" sheetId="1" r:id="rId1"/>
@@ -14914,6 +14914,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G103"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="255.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -16246,6 +16249,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D103"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="57.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -22663,6 +22671,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F765"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.109375" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -37973,6 +37989,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:U111"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
